--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6911,7 +6911,7 @@
         <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>140</v>
